--- a/02_Test_Cases/TC_Module03_Checkout.xlsx
+++ b/02_Test_Cases/TC_Module03_Checkout.xlsx
@@ -9,109 +9,55 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="CXtoJkoeTM5xmFRFSMc5EgYk7xgNKURvvsZXzjwU0b8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="z9VMvOi28pMiosxqWbbZCsWei/ubKcuz7/FoHUM9pEA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="120">
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>Tên Test Case</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="68">
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>Tiêu đề (Title)</t>
   </si>
   <si>
     <t>Điều kiện trước</t>
   </si>
   <si>
-    <t>Các bước</t>
-  </si>
-  <si>
-    <t>Dữ liệu test</t>
+    <t>Các bước thực hiện</t>
   </si>
   <si>
     <t>Kết quả mong đợi</t>
   </si>
   <si>
-    <t>Loại</t>
-  </si>
-  <si>
-    <t>TC_ID</t>
-  </si>
-  <si>
-    <t>Tiêu đề (Title)</t>
-  </si>
-  <si>
-    <t>Các bước thực hiện</t>
-  </si>
-  <si>
     <t>Loại (Type)</t>
   </si>
   <si>
     <t>Độ ưu tiên</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_001</t>
-  </si>
-  <si>
-    <t>Checkout với thông tin hợp lệ</t>
-  </si>
-  <si>
-    <t>Có sản phẩm trong cart</t>
-  </si>
-  <si>
-    <t>Checkout → nhập thông tin</t>
-  </si>
-  <si>
-    <t>valid address</t>
-  </si>
-  <si>
-    <t>Đặt hàng thành công</t>
+    <t>TC_CHKT_001</t>
+  </si>
+  <si>
+    <t>Nhập địa chỉ giao hàng hợp lệ</t>
+  </si>
+  <si>
+    <t>Giỏ hàng có SP, đã nhấn Checkout</t>
+  </si>
+  <si>
+    <t>1. Nhập đầy đủ các trường: Address, City, State, Postcode, Mobile Number.</t>
+  </si>
+  <si>
+    <t>Hệ thống chấp nhận thông tin, cho phép chuyển sang bước tiếp theo.</t>
   </si>
   <si>
     <t>Positive</t>
   </si>
   <si>
-    <t>TC_CHKT_001</t>
-  </si>
-  <si>
-    <t>Nhập địa chỉ giao hàng hợp lệ</t>
-  </si>
-  <si>
-    <t>Giỏ hàng có SP, đã nhấn Checkout</t>
-  </si>
-  <si>
-    <t>1. Nhập đầy đủ các trường: Address, City, State, Postcode, Mobile Number.</t>
-  </si>
-  <si>
-    <t>Hệ thống chấp nhận thông tin, cho phép chuyển sang bước tiếp theo.</t>
-  </si>
-  <si>
     <t>High</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_002</t>
-  </si>
-  <si>
-    <t>Checkout khi giỏ hàng trống</t>
-  </si>
-  <si>
-    <t>Không có sản phẩm</t>
-  </si>
-  <si>
-    <t>Click checkout</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Không cho checkout</t>
-  </si>
-  <si>
-    <t>Negative</t>
   </si>
   <si>
     <t>TC_CHKT_002</t>
@@ -127,22 +73,7 @@
     <t>Hệ thống báo lỗi: "Please fill in this field" hoặc tương tự.</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_003</t>
-  </si>
-  <si>
-    <t>Thanh toán thẻ hợp lệ</t>
-  </si>
-  <si>
-    <t>Có sản phẩm</t>
-  </si>
-  <si>
-    <t>Nhập card hợp lệ</t>
-  </si>
-  <si>
-    <t>Visa</t>
-  </si>
-  <si>
-    <t>Thanh toán thành công</t>
+    <t>Negative</t>
   </si>
   <si>
     <t>TC_CHKT_003</t>
@@ -164,21 +95,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_004</t>
-  </si>
-  <si>
-    <t>Thanh toán thiếu số thẻ</t>
-  </si>
-  <si>
-    <t>Không nhập card number</t>
-  </si>
-  <si>
-    <t>empty</t>
-  </si>
-  <si>
-    <t>Hiển thị lỗi</t>
-  </si>
-  <si>
     <t>TC_CHKT_004</t>
   </si>
   <si>
@@ -191,24 +107,12 @@
     <t>Hệ thống ghi nhận phương thức thanh toán là tiền mặt.</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_005</t>
-  </si>
-  <si>
-    <t>Thanh toán thẻ hết hạn</t>
-  </si>
-  <si>
-    <t>Nhập thẻ hết hạn</t>
-  </si>
-  <si>
-    <t>expired card</t>
-  </si>
-  <si>
-    <t>Thanh toán thất bại</t>
-  </si>
-  <si>
     <t>TC_CHKT_005</t>
   </si>
   <si>
+    <t>Đặt hàng thành công</t>
+  </si>
+  <si>
     <t>Thông tin đầy đủ</t>
   </si>
   <si>
@@ -216,24 +120,6 @@
   </si>
   <si>
     <t>Hiển thị thông báo "ORDER PLACED!" và mã đơn hàng.</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_006</t>
-  </si>
-  <si>
-    <t>Nhập địa chỉ rất dài</t>
-  </si>
-  <si>
-    <t>Nhập address 200 ký tự</t>
-  </si>
-  <si>
-    <t>long text</t>
-  </si>
-  <si>
-    <t>Hệ thống chấp nhận</t>
-  </si>
-  <si>
-    <t>Boundary</t>
   </si>
   <si>
     <t>TC_CHKT_006</t>
@@ -252,15 +138,6 @@
     <t>Hệ thống chặn lại và yêu cầu nhập thông tin thẻ.</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_007</t>
-  </si>
-  <si>
-    <t>Checkout bỏ trống địa chỉ</t>
-  </si>
-  <si>
-    <t>Không nhập address</t>
-  </si>
-  <si>
     <t>TC_CHKT_007</t>
   </si>
   <si>
@@ -273,18 +150,12 @@
     <t>Hệ thống xử lý theo quy định (thường là báo lỗi nếu quá dài/ngắn).</t>
   </si>
   <si>
+    <t>Boundary</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_008</t>
-  </si>
-  <si>
-    <t>Nhập số thẻ quá ngắn</t>
-  </si>
-  <si>
-    <t>Nhập card number 3 số</t>
-  </si>
-  <si>
     <t>TC_CHKT_008</t>
   </si>
   <si>
@@ -297,21 +168,6 @@
     <t>Hệ thống báo lỗi thẻ không hợp lệ/hết hạn.</t>
   </si>
   <si>
-    <t>TC_CHECKOUT_009</t>
-  </si>
-  <si>
-    <t>Xác nhận đơn hàng</t>
-  </si>
-  <si>
-    <t>Thanh toán xong</t>
-  </si>
-  <si>
-    <t>Click Confirm Order</t>
-  </si>
-  <si>
-    <t>Hiển thị Order Success</t>
-  </si>
-  <si>
     <t>TC_CHKT_009</t>
   </si>
   <si>
@@ -322,18 +178,6 @@
   </si>
   <si>
     <t>Hệ thống chỉ xử lý 1 đơn hàng, không tạo đơn trùng.</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_010</t>
-  </si>
-  <si>
-    <t>Hủy checkout</t>
-  </si>
-  <si>
-    <t>Click Cancel</t>
-  </si>
-  <si>
-    <t>Quay lại giỏ hàng</t>
   </si>
   <si>
     <t>TC_ACC_001</t>
@@ -386,7 +230,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -395,19 +239,8 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF1F1F1F"/>
@@ -428,18 +261,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -655,22 +484,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="23.29"/>
-    <col customWidth="1" min="2" max="2" width="36.29"/>
-    <col customWidth="1" min="3" max="3" width="27.43"/>
-    <col customWidth="1" min="4" max="4" width="28.43"/>
-    <col customWidth="1" min="5" max="5" width="15.43"/>
-    <col customWidth="1" min="6" max="6" width="23.43"/>
-    <col customWidth="1" min="7" max="7" width="12.0"/>
-    <col customWidth="1" min="8" max="8" width="8.71"/>
-    <col customWidth="1" min="9" max="9" width="16.86"/>
-    <col customWidth="1" min="10" max="10" width="15.14"/>
-    <col customWidth="1" min="11" max="11" width="19.0"/>
-    <col customWidth="1" min="12" max="12" width="24.14"/>
-    <col customWidth="1" min="13" max="13" width="20.14"/>
-    <col customWidth="1" min="14" max="14" width="12.57"/>
-    <col customWidth="1" min="15" max="15" width="14.0"/>
-    <col customWidth="1" min="16" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="16.86"/>
+    <col customWidth="1" min="2" max="2" width="15.14"/>
+    <col customWidth="1" min="3" max="3" width="19.0"/>
+    <col customWidth="1" min="4" max="4" width="24.14"/>
+    <col customWidth="1" min="5" max="5" width="20.14"/>
+    <col customWidth="1" min="6" max="6" width="12.57"/>
+    <col customWidth="1" min="7" max="7" width="14.0"/>
+    <col customWidth="1" min="8" max="18" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -695,531 +516,281 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>24</v>
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>47</v>
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>47</v>
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>24</v>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>24</v>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="A8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" s="3">
-        <v>123.0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O9" s="4" t="s">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>47</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="A10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>24</v>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>24</v>
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>47</v>
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="I13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>84</v>
+      <c r="A13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1"/>
